--- a/data/trans_dic/P37A$vacunaempresa-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P37A$vacunaempresa-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,79</t>
+          <t>0,18; 1,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,38</t>
+          <t>0,51; 3,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 5,24</t>
+          <t>0,0; 3,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,97</t>
+          <t>1,56; 6,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,03</t>
+          <t>0,11; 0,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,89</t>
+          <t>0,34; 1,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,57</t>
+          <t>1,19; 4,06</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,33</t>
+          <t>0,63; 2,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,37</t>
+          <t>0,7; 2,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,01</t>
+          <t>0,34; 2,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,56</t>
+          <t>0,8; 4,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,48</t>
+          <t>0,51; 2,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,99</t>
+          <t>0,79; 3,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,43</t>
+          <t>0,15; 1,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,89</t>
+          <t>2,23; 5,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,96</t>
+          <t>0,71; 1,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,38</t>
+          <t>0,96; 2,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,43</t>
+          <t>0,34; 1,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,47</t>
+          <t>1,93; 4,33</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,62</t>
+          <t>1,1; 3,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,49</t>
+          <t>1,19; 3,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,4</t>
+          <t>2,46; 5,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,73</t>
+          <t>0,29; 1,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,13</t>
+          <t>0,95; 2,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,32</t>
+          <t>0,56; 2,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,21</t>
+          <t>2,53; 5,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,19</t>
+          <t>0,86; 2,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,75</t>
+          <t>1,22; 2,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,34</t>
+          <t>0,37; 1,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,38</t>
+          <t>2,84; 4,83</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,56</t>
+          <t>0,57; 2,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,43</t>
+          <t>0,86; 3,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,55</t>
+          <t>3,44; 6,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,16</t>
+          <t>0,31; 2,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,96</t>
+          <t>0,17; 2,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,57</t>
+          <t>3,68; 6,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,4</t>
+          <t>0,28; 1,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,49</t>
+          <t>0,75; 2,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,46</t>
+          <t>0,31; 1,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,56</t>
+          <t>4,0; 6,16</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -1277,27 +1277,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,85</t>
+          <t>0,22; 2,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,98</t>
+          <t>0,25; 3,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,46</t>
+          <t>0,22; 2,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,61</t>
+          <t>1,72; 4,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,01</t>
+          <t>0,23; 1,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,99</t>
+          <t>2,57; 5,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,53</t>
+          <t>0,24; 1,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,82</t>
+          <t>0,24; 1,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,52</t>
+          <t>0,24; 1,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,34</t>
+          <t>2,44; 4,22</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,02</t>
+          <t>0,3; 2,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,83</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1452,17 +1452,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,73</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,93</t>
+          <t>0,23; 1,13</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,44</t>
+          <t>0,12; 1,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,95</t>
+          <t>0,07; 0,93</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,47</t>
+          <t>0,75; 1,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1707,52 +1707,52 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,78</t>
+          <t>0,26; 0,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,2</t>
+          <t>2,18; 3,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,84</t>
+          <t>0,33; 0,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,23</t>
+          <t>0,58; 1,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,84</t>
+          <t>0,32; 0,81</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,54</t>
+          <t>2,7; 3,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,99</t>
+          <t>0,59; 1,02</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,41</t>
+          <t>0,87; 1,44</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,69</t>
+          <t>0,34; 0,71</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,38; 3,28</t>
+          <t>2,57; 3,38</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>12349</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17864</t>
+          <t>17649</t>
         </is>
       </c>
     </row>
@@ -2068,12 +2068,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>901; 8854</t>
+          <t>896; 8019</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2082; 15357</t>
+          <t>2313; 17245</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2083,47 +2083,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1251; 20961</t>
+          <t>0; 15025</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4500</t>
+          <t>0; 4002</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5523</t>
+          <t>0; 5626</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4695</t>
+          <t>0; 4725</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5108; 21838</t>
+          <t>5639; 22666</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>923; 9867</t>
+          <t>1068; 8933</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2974; 16750</t>
+          <t>2997; 15654</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5098</t>
+          <t>0; 5371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8460; 32596</t>
+          <t>9178; 31298</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8945</t>
+          <t>10233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>19538</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27554</t>
+          <t>29771</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4820; 17148</t>
+          <t>4655; 17339</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4738; 16273</t>
+          <t>4801; 17059</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2040; 11896</t>
+          <t>2012; 11957</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3237; 19328</t>
+          <t>3836; 20195</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3157; 15531</t>
+          <t>3168; 13998</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4816; 18232</t>
+          <t>4845; 19020</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>846; 8080</t>
+          <t>841; 8521</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9481; 30143</t>
+          <t>11174; 29263</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9608; 26741</t>
+          <t>9672; 26547</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12340; 30834</t>
+          <t>12457; 29959</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3881; 16526</t>
+          <t>3920; 16651</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17585; 41836</t>
+          <t>18881; 42384</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22865</t>
+          <t>23814</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21965</t>
+          <t>22936</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44830</t>
+          <t>46749</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6923; 23138</t>
+          <t>7048; 22624</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8297; 23811</t>
+          <t>8126; 23486</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6130</t>
+          <t>0; 6123</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14226; 34316</t>
+          <t>15250; 37169</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1992; 11902</t>
+          <t>1982; 11829</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6125; 22280</t>
+          <t>6721; 21183</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3594; 15331</t>
+          <t>3686; 16079</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14675; 30815</t>
+          <t>15797; 32132</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11399; 29103</t>
+          <t>11442; 29908</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17516; 38312</t>
+          <t>16997; 38544</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4584; 17863</t>
+          <t>4960; 17664</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33902; 60659</t>
+          <t>35280; 60077</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31938</t>
+          <t>34440</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>35853</t>
+          <t>36732</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67791</t>
+          <t>71172</t>
         </is>
       </c>
     </row>
@@ -2692,22 +2692,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2965; 13266</t>
+          <t>2967; 13715</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5138; 21056</t>
+          <t>5280; 23476</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1002; 11427</t>
+          <t>1005; 11424</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12725; 49269</t>
+          <t>24092; 48255</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2717,37 +2717,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1114; 13290</t>
+          <t>1934; 13508</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1825; 12731</t>
+          <t>1097; 13240</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27845; 46829</t>
+          <t>27115; 45180</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2978; 14511</t>
+          <t>2891; 14068</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9245; 30622</t>
+          <t>9257; 29002</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3976; 18966</t>
+          <t>3953; 18294</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42927; 89000</t>
+          <t>57526; 88481</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>17397</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19887</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36488</t>
+          <t>39646</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>841; 7171</t>
+          <t>852; 8071</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1091; 12785</t>
+          <t>1095; 14558</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1052; 11777</t>
+          <t>1052; 11079</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10253; 25892</t>
+          <t>10481; 26715</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>922; 8140</t>
+          <t>921; 7669</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5323</t>
+          <t>0; 5334</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 8120</t>
+          <t>0; 7055</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13936; 27336</t>
+          <t>15659; 30522</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1907; 12124</t>
+          <t>1907; 11329</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2149; 15929</t>
+          <t>2126; 14064</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2234; 14782</t>
+          <t>2325; 14732</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27724; 48135</t>
+          <t>29705; 51405</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4846</t>
         </is>
       </c>
     </row>
@@ -3123,17 +3123,17 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1237; 7447</t>
+          <t>1217; 8138</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6291</t>
+          <t>0; 6049</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4862</t>
+          <t>0; 4845</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4397</t>
+          <t>0; 4270</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4480</t>
+          <t>0; 4500</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4862</t>
+          <t>0; 5502</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1483; 9072</t>
+          <t>1937; 9535</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2376</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>477; 6116</t>
+          <t>543; 7226</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>475; 6699</t>
+          <t>539; 7183</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>90082</t>
+          <t>94807</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>110929</t>
+          <t>117402</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>201011</t>
+          <t>212209</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>24270; 48014</t>
+          <t>24584; 48567</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>34617; 64547</t>
+          <t>34748; 64513</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9042; 26472</t>
+          <t>8886; 25994</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>67409; 110563</t>
+          <t>77178; 116429</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>11597; 28389</t>
+          <t>10996; 28172</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21545; 43891</t>
+          <t>20789; 44556</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11815; 29907</t>
+          <t>11466; 28883</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>86964; 131265</t>
+          <t>100735; 139588</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>39283; 66045</t>
+          <t>39214; 68139</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>60565; 98393</t>
+          <t>61116; 100264</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>23057; 47937</t>
+          <t>23846; 49113</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>170575; 235060</t>
+          <t>187093; 245828</t>
         </is>
       </c>
     </row>
